--- a/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
+++ b/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
@@ -1144,7 +1144,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1171,11 +1171,11 @@
     <col min="30" max="30" width="2.66666666666667" style="1" customWidth="1"/>
     <col min="31" max="32" width="10.8888888888889" style="1"/>
     <col min="33" max="33" width="2.66666666666667" style="1" customWidth="1"/>
-    <col min="34" max="34" width="10.8888888888889" style="1"/>
-    <col min="35" max="16384" width="9" style="1"/>
+    <col min="34" max="35" width="10.8888888888889" style="1"/>
+    <col min="36" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1232,6 +1232,9 @@
       </c>
       <c r="AH1" s="5">
         <v>46004</v>
+      </c>
+      <c r="AI1" s="5">
+        <v>46018</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -1302,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:36">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1393,8 +1396,14 @@
       <c r="AG3" s="1">
         <v>3</v>
       </c>
+      <c r="AI3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:36">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1457,6 +1466,12 @@
       </c>
       <c r="AG4" s="1">
         <v>2</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -1554,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:36">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1615,8 +1630,14 @@
       <c r="AG6" s="1">
         <v>2</v>
       </c>
+      <c r="AI6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>7</v>
+      </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:36">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1713,8 +1734,14 @@
       <c r="AG7" s="1">
         <v>3</v>
       </c>
+      <c r="AI7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>6</v>
+      </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:36">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -1766,8 +1793,14 @@
       <c r="AG8" s="1">
         <v>2</v>
       </c>
+      <c r="AI8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:36">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1855,8 +1888,14 @@
       <c r="AG9" s="1">
         <v>0</v>
       </c>
+      <c r="AI9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:36">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1940,6 +1979,12 @@
       </c>
       <c r="AH10" s="1">
         <v>1</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -2078,7 +2123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:36">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -2154,8 +2199,14 @@
       <c r="AH13" s="1">
         <v>1</v>
       </c>
+      <c r="AI13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>6</v>
+      </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:36">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -2242,6 +2293,12 @@
       </c>
       <c r="AH14" s="1">
         <v>1</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:34">

--- a/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
+++ b/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="21996" windowHeight="9227"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>Педагог</t>
   </si>
@@ -1144,7 +1144,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1172,10 +1172,12 @@
     <col min="31" max="32" width="10.8888888888889" style="1"/>
     <col min="33" max="33" width="2.66666666666667" style="1" customWidth="1"/>
     <col min="34" max="35" width="10.8888888888889" style="1"/>
-    <col min="36" max="16384" width="9" style="1"/>
+    <col min="36" max="36" width="2.66666666666667" style="1" customWidth="1"/>
+    <col min="37" max="37" width="10.8888888888889" style="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:37">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1235,6 +1237,9 @@
       </c>
       <c r="AI1" s="5">
         <v>46018</v>
+      </c>
+      <c r="AK1" s="5">
+        <v>46380</v>
       </c>
     </row>
     <row r="2" spans="1:34">
@@ -1305,7 +1310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:37">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1402,8 +1407,11 @@
       <c r="AJ3" s="1">
         <v>7</v>
       </c>
+      <c r="AK3" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:37">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1473,8 +1481,11 @@
       <c r="AJ4" s="1">
         <v>5</v>
       </c>
+      <c r="AK4" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:37">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1568,8 +1579,11 @@
       <c r="AH5" s="1">
         <v>1</v>
       </c>
+      <c r="AK5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:37">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1636,8 +1650,11 @@
       <c r="AJ6" s="1">
         <v>7</v>
       </c>
+      <c r="AK6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:37">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1740,8 +1757,11 @@
       <c r="AJ7" s="1">
         <v>6</v>
       </c>
+      <c r="AK7" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:37">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -1799,8 +1819,11 @@
       <c r="AJ8" s="1">
         <v>2</v>
       </c>
+      <c r="AK8" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:37">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1894,8 +1917,11 @@
       <c r="AJ9" s="1">
         <v>4</v>
       </c>
+      <c r="AK9" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:36">
+    <row r="10" spans="1:37">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1985,6 +2011,9 @@
       </c>
       <c r="AJ10" s="1">
         <v>5</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -2064,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:37">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
@@ -2122,8 +2151,11 @@
       <c r="AG12" s="1">
         <v>1</v>
       </c>
+      <c r="AK12" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:37">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -2205,8 +2237,11 @@
       <c r="AJ13" s="1">
         <v>6</v>
       </c>
+      <c r="AK13" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:37">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -2299,6 +2334,9 @@
       </c>
       <c r="AJ14" s="1">
         <v>7</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:34">
@@ -2375,7 +2413,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:33">
+    <row r="16" spans="1:37">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
@@ -2393,6 +2434,9 @@
       </c>
       <c r="AG16" s="1">
         <v>3</v>
+      </c>
+      <c r="AK16" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18">

--- a/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
+++ b/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21996" windowHeight="9227"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$N$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
   <si>
     <t>Педагог</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Биофизика</t>
   </si>
   <si>
+    <t>ИТОГО</t>
+  </si>
+  <si>
     <t>ВМ</t>
   </si>
   <si>
@@ -56,21 +59,33 @@
     <t>Архарова</t>
   </si>
   <si>
+    <t>Protista</t>
+  </si>
+  <si>
     <t>Ульяна</t>
   </si>
   <si>
     <t>Попова</t>
   </si>
   <si>
+    <t>Porifera</t>
+  </si>
+  <si>
     <t>Артём</t>
   </si>
   <si>
     <t>Темнов</t>
   </si>
   <si>
+    <t>Ctenophora</t>
+  </si>
+  <si>
     <t>Стовбур</t>
   </si>
   <si>
+    <t>Coelenterata</t>
+  </si>
+  <si>
     <t>Александра</t>
   </si>
   <si>
@@ -135,6 +150,12 @@
   </si>
   <si>
     <t>Тепляков</t>
+  </si>
+  <si>
+    <t>Станислав</t>
+  </si>
+  <si>
+    <t>Абрамов</t>
   </si>
   <si>
     <t>Герман</t>
@@ -817,13 +838,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1144,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK28"/>
+  <dimension ref="A1:AT29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1173,11 +1195,17 @@
     <col min="33" max="33" width="2.66666666666667" style="1" customWidth="1"/>
     <col min="34" max="35" width="10.8888888888889" style="1"/>
     <col min="36" max="36" width="2.66666666666667" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.8888888888889" style="1"/>
-    <col min="38" max="16384" width="9" style="1"/>
+    <col min="37" max="39" width="10.8888888888889" style="1"/>
+    <col min="40" max="40" width="3.66666666666667" style="1" customWidth="1"/>
+    <col min="41" max="41" width="10.8888888888889" style="1"/>
+    <col min="42" max="42" width="3.66666666666667" style="1" customWidth="1"/>
+    <col min="43" max="43" width="9" style="1"/>
+    <col min="44" max="44" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="45" max="46" width="10.8888888888889" style="1"/>
+    <col min="47" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:46">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1241,16 +1269,34 @@
       <c r="AK1" s="5">
         <v>46380</v>
       </c>
+      <c r="AL1" s="5">
+        <v>46053</v>
+      </c>
+      <c r="AM1" s="5">
+        <v>46060</v>
+      </c>
+      <c r="AO1" s="5">
+        <v>46067</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS1" s="5">
+        <v>46074</v>
+      </c>
+      <c r="AT1" s="5">
+        <v>46081</v>
+      </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:46">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -1309,16 +1355,44 @@
       <c r="AH2" s="1">
         <v>1</v>
       </c>
+      <c r="AL2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>16</v>
+      </c>
+      <c r="AQ2" s="6">
+        <f>SUM(D2:AP2)</f>
+        <v>27</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:44">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -1410,16 +1484,32 @@
       <c r="AK3" s="1">
         <v>1</v>
       </c>
+      <c r="AL3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AQ3" s="6">
+        <f t="shared" ref="AQ3:AQ17" si="0">SUM(D3:AP3)</f>
+        <v>34</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:45">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -1484,16 +1574,41 @@
       <c r="AK4" s="1">
         <v>1</v>
       </c>
+      <c r="AL4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>14</v>
+      </c>
+      <c r="AQ4" s="6">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:46">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1582,16 +1697,44 @@
       <c r="AK5" s="1">
         <v>1</v>
       </c>
+      <c r="AL5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>23</v>
+      </c>
+      <c r="AQ5" s="6">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:46">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -1653,16 +1796,38 @@
       <c r="AK6" s="1">
         <v>1</v>
       </c>
+      <c r="AL6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AQ6" s="6">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:46">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1760,16 +1925,35 @@
       <c r="AK7" s="1">
         <v>1</v>
       </c>
+      <c r="AL7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AQ7" s="6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:46">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1822,16 +2006,35 @@
       <c r="AK8" s="1">
         <v>1</v>
       </c>
+      <c r="AL8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AQ8" s="6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:46">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -1920,16 +2123,35 @@
       <c r="AK9" s="1">
         <v>1</v>
       </c>
+      <c r="AL9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AQ9" s="6">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:46">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2015,16 +2237,44 @@
       <c r="AK10" s="1">
         <v>1</v>
       </c>
+      <c r="AL10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>23</v>
+      </c>
+      <c r="AQ10" s="6">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:44">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -2092,16 +2342,26 @@
       <c r="AB11" s="1">
         <v>0</v>
       </c>
+      <c r="AN11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="6">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:45">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -2154,16 +2414,41 @@
       <c r="AK12" s="1">
         <v>1</v>
       </c>
+      <c r="AL12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>24</v>
+      </c>
+      <c r="AQ12" s="6">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:46">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -2240,16 +2525,44 @@
       <c r="AK13" s="1">
         <v>1</v>
       </c>
+      <c r="AL13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>19</v>
+      </c>
+      <c r="AQ13" s="6">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="AR13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:46">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2338,16 +2651,44 @@
       <c r="AK14" s="1">
         <v>1</v>
       </c>
+      <c r="AL14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP14" s="1">
+        <v>26</v>
+      </c>
+      <c r="AQ14" s="6">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:44">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H15" s="1">
         <v>1</v>
@@ -2412,16 +2753,26 @@
       <c r="AH15" s="1">
         <v>1</v>
       </c>
+      <c r="AN15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="6">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AR15" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:45">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AC16" s="1">
         <v>1</v>
@@ -2438,30 +2789,78 @@
       <c r="AK16" s="1">
         <v>1</v>
       </c>
+      <c r="AL16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="1">
+        <v>10</v>
+      </c>
+      <c r="AQ16" s="6">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="AR16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS16" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
+    <row r="17" spans="1:46">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AM17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN17" s="1">
+        <v>-5</v>
+      </c>
+      <c r="AO17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="1">
+        <v>13</v>
+      </c>
+      <c r="AQ17" s="6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="AR17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="R20" s="1">
         <v>0</v>
@@ -2469,13 +2868,13 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R21" s="1">
         <v>0</v>
@@ -2483,13 +2882,13 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
@@ -2497,13 +2896,13 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="R23" s="1">
         <v>0</v>
@@ -2511,13 +2910,13 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="R24" s="1">
         <v>0</v>
@@ -2525,13 +2924,13 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
@@ -2539,13 +2938,13 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="R26" s="1">
         <v>0</v>
@@ -2553,13 +2952,13 @@
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R27" s="1">
         <v>0</v>
@@ -2567,20 +2966,34 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="R28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="R29" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N16" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N17" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
+++ b/Рабочие материалы/Реальные группы 2025-2026/новички_2025.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$N$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -116,97 +116,97 @@
     <t>Бойцов</t>
   </si>
   <si>
+    <t>Алексей</t>
+  </si>
+  <si>
+    <t>Хрипунков</t>
+  </si>
+  <si>
+    <t>Григорий</t>
+  </si>
+  <si>
+    <t>Бекасов</t>
+  </si>
+  <si>
+    <t>Назар</t>
+  </si>
+  <si>
+    <t>Ляховецкий</t>
+  </si>
+  <si>
+    <t>Кирилл</t>
+  </si>
+  <si>
+    <t>Тепляков</t>
+  </si>
+  <si>
+    <t>Станислав</t>
+  </si>
+  <si>
+    <t>Абрамов</t>
+  </si>
+  <si>
+    <t>Герман</t>
+  </si>
+  <si>
+    <t>Соколов</t>
+  </si>
+  <si>
+    <t>Леонид</t>
+  </si>
+  <si>
+    <t>Анастасия</t>
+  </si>
+  <si>
+    <t>Ригина</t>
+  </si>
+  <si>
+    <t>Михаил</t>
+  </si>
+  <si>
+    <t>Бирюков</t>
+  </si>
+  <si>
+    <t>Александр</t>
+  </si>
+  <si>
+    <t>Хижняков</t>
+  </si>
+  <si>
+    <t>Захарова</t>
+  </si>
+  <si>
+    <t>Марина</t>
+  </si>
+  <si>
+    <t>Федотова</t>
+  </si>
+  <si>
+    <t>Кузьмин</t>
+  </si>
+  <si>
+    <t>Ярослав</t>
+  </si>
+  <si>
+    <t>Зенцов</t>
+  </si>
+  <si>
+    <t>Софья</t>
+  </si>
+  <si>
+    <t>Плечева</t>
+  </si>
+  <si>
     <t>Тимур</t>
   </si>
   <si>
     <t>Просверницын</t>
   </si>
   <si>
-    <t>Алексей</t>
-  </si>
-  <si>
-    <t>Хрипунков</t>
-  </si>
-  <si>
-    <t>Григорий</t>
-  </si>
-  <si>
-    <t>Бекасов</t>
-  </si>
-  <si>
-    <t>Назар</t>
-  </si>
-  <si>
-    <t>Ляховецкий</t>
-  </si>
-  <si>
     <t>Егор</t>
   </si>
   <si>
     <t>Илюшкин</t>
-  </si>
-  <si>
-    <t>Кирилл</t>
-  </si>
-  <si>
-    <t>Тепляков</t>
-  </si>
-  <si>
-    <t>Станислав</t>
-  </si>
-  <si>
-    <t>Абрамов</t>
-  </si>
-  <si>
-    <t>Герман</t>
-  </si>
-  <si>
-    <t>Соколов</t>
-  </si>
-  <si>
-    <t>Леонид</t>
-  </si>
-  <si>
-    <t>Анастасия</t>
-  </si>
-  <si>
-    <t>Ригина</t>
-  </si>
-  <si>
-    <t>Михаил</t>
-  </si>
-  <si>
-    <t>Бирюков</t>
-  </si>
-  <si>
-    <t>Александр</t>
-  </si>
-  <si>
-    <t>Хижняков</t>
-  </si>
-  <si>
-    <t>Захарова</t>
-  </si>
-  <si>
-    <t>Марина</t>
-  </si>
-  <si>
-    <t>Федотова</t>
-  </si>
-  <si>
-    <t>Кузьмин</t>
-  </si>
-  <si>
-    <t>Ярослав</t>
-  </si>
-  <si>
-    <t>Зенцов</t>
-  </si>
-  <si>
-    <t>Софья</t>
-  </si>
-  <si>
-    <t>Плечева</t>
   </si>
 </sst>
 </file>
@@ -843,8 +843,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
@@ -1166,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AT29"/>
+  <dimension ref="A1:BG29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1201,11 +1201,20 @@
     <col min="42" max="42" width="3.66666666666667" style="1" customWidth="1"/>
     <col min="43" max="43" width="9" style="1"/>
     <col min="44" max="44" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="45" max="46" width="10.8888888888889" style="1"/>
-    <col min="47" max="16384" width="9" style="1"/>
+    <col min="45" max="47" width="10.8888888888889" style="1"/>
+    <col min="48" max="49" width="2.66666666666667" style="1" customWidth="1"/>
+    <col min="50" max="50" width="10.8888888888889" style="1"/>
+    <col min="51" max="51" width="2.66666666666667" style="1" customWidth="1"/>
+    <col min="52" max="54" width="10.8888888888889" style="1"/>
+    <col min="55" max="55" width="2.66666666666667" style="1" customWidth="1"/>
+    <col min="56" max="56" width="4.66666666666667" style="1" customWidth="1"/>
+    <col min="57" max="57" width="3.66666666666667" style="1" customWidth="1"/>
+    <col min="58" max="58" width="2.66666666666667" style="1" customWidth="1"/>
+    <col min="59" max="59" width="10.8888888888889" style="1"/>
+    <col min="60" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46">
+    <row r="1" spans="1:59">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1227,13 +1236,13 @@
       <c r="H1" s="3">
         <v>45941</v>
       </c>
-      <c r="M1" s="5">
+      <c r="M1" s="4">
         <v>45948</v>
       </c>
-      <c r="S1" s="5">
+      <c r="S1" s="4">
         <v>45955</v>
       </c>
-      <c r="T1" s="5">
+      <c r="T1" s="4">
         <v>45959</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -1242,60 +1251,78 @@
       <c r="V1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="W1" s="5">
+      <c r="W1" s="4">
         <v>45969</v>
       </c>
-      <c r="X1" s="5">
+      <c r="X1" s="4">
         <v>45976</v>
       </c>
       <c r="AA1" s="1">
         <v>-1</v>
       </c>
-      <c r="AC1" s="5">
+      <c r="AC1" s="4">
         <v>45983</v>
       </c>
-      <c r="AE1" s="5">
+      <c r="AE1" s="4">
         <v>45990</v>
       </c>
-      <c r="AF1" s="5">
+      <c r="AF1" s="4">
         <v>45997</v>
       </c>
-      <c r="AH1" s="5">
+      <c r="AH1" s="4">
         <v>46004</v>
       </c>
-      <c r="AI1" s="5">
+      <c r="AI1" s="4">
         <v>46018</v>
       </c>
-      <c r="AK1" s="5">
+      <c r="AK1" s="4">
         <v>46380</v>
       </c>
-      <c r="AL1" s="5">
+      <c r="AL1" s="4">
         <v>46053</v>
       </c>
-      <c r="AM1" s="5">
+      <c r="AM1" s="4">
         <v>46060</v>
       </c>
-      <c r="AO1" s="5">
+      <c r="AO1" s="4">
         <v>46067</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AS1" s="5">
+      <c r="AS1" s="4">
         <v>46074</v>
       </c>
-      <c r="AT1" s="5">
+      <c r="AT1" s="4">
         <v>46081</v>
       </c>
+      <c r="AU1" s="4">
+        <v>46088</v>
+      </c>
+      <c r="AX1" s="4">
+        <v>46095</v>
+      </c>
+      <c r="AZ1" s="4">
+        <v>46102</v>
+      </c>
+      <c r="BA1" s="4">
+        <v>46109</v>
+      </c>
+      <c r="BB1" s="4">
+        <v>45747</v>
+      </c>
+      <c r="BG1" s="4">
+        <v>46123</v>
+      </c>
     </row>
-    <row r="2" spans="1:46">
+    <row r="2" spans="1:59">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1">
@@ -1383,15 +1410,30 @@
       <c r="AT2" s="1">
         <v>1</v>
       </c>
+      <c r="AU2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:44">
+    <row r="3" spans="1:59">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="1">
@@ -1500,15 +1542,42 @@
       <c r="AR3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AU3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>-12</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>5</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:45">
+    <row r="4" spans="1:59">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="1">
@@ -1599,15 +1668,30 @@
       <c r="AS4" s="1">
         <v>1</v>
       </c>
+      <c r="AU4" s="1">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG4" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:59">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="1">
@@ -1725,15 +1809,42 @@
       <c r="AT5" s="1">
         <v>1</v>
       </c>
+      <c r="AU5" s="1">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>2</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>2</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>-6</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>9</v>
+      </c>
+      <c r="BF5" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:59">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="1">
@@ -1818,15 +1929,21 @@
       <c r="AT6" s="1">
         <v>1</v>
       </c>
+      <c r="AU6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:59">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="1">
@@ -1944,15 +2061,45 @@
       <c r="AT7" s="1">
         <v>1</v>
       </c>
+      <c r="AU7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>2</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>8</v>
+      </c>
+      <c r="BE7" s="1">
+        <v>5</v>
+      </c>
+      <c r="BG7" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:59">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="1">
@@ -2025,15 +2172,21 @@
       <c r="AT8" s="1">
         <v>1</v>
       </c>
+      <c r="AZ8" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA8" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:59">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="1">
@@ -2142,15 +2295,39 @@
       <c r="AT9" s="1">
         <v>1</v>
       </c>
+      <c r="AU9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="1">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC9" s="1">
+        <v>2</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>-4</v>
+      </c>
+      <c r="BE9" s="1">
+        <v>3</v>
+      </c>
+      <c r="BF9" s="1">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:59">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="1">
@@ -2265,44 +2442,35 @@
       <c r="AT10" s="1">
         <v>1</v>
       </c>
+      <c r="AU10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG10" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:44">
+    <row r="11" spans="1:59">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>4</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>2</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
       <c r="M11" s="1">
         <v>1</v>
       </c>
@@ -2310,25 +2478,16 @@
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="1">
         <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>1</v>
-      </c>
-      <c r="T11" s="1">
-        <v>2</v>
-      </c>
-      <c r="U11" s="1">
-        <v>2</v>
-      </c>
-      <c r="V11" s="1">
-        <v>2</v>
+        <v>-1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>1</v>
       </c>
       <c r="X11" s="1">
         <v>1</v>
@@ -2337,52 +2496,124 @@
         <v>10</v>
       </c>
       <c r="Z11" s="1">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB11" s="1">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>1</v>
       </c>
       <c r="AN11" s="1">
         <v>0</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>24</v>
       </c>
       <c r="AQ11" s="6">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AR11" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="1">
+        <v>3</v>
+      </c>
+      <c r="BB11" s="1">
+        <v>2</v>
+      </c>
+      <c r="BC11" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="1">
+        <v>-6</v>
+      </c>
+      <c r="BE11" s="1">
+        <v>13</v>
+      </c>
+      <c r="BF11" s="1">
+        <v>5</v>
+      </c>
+      <c r="BG11" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:45">
+    <row r="12" spans="1:59">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>-3</v>
+      </c>
+      <c r="L12" s="1">
+        <v>-2</v>
       </c>
       <c r="R12" s="1">
-        <v>-1</v>
-      </c>
-      <c r="W12" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>2</v>
+      </c>
+      <c r="U12" s="1">
+        <v>2</v>
       </c>
       <c r="X12" s="1">
         <v>1</v>
@@ -2391,25 +2622,34 @@
         <v>10</v>
       </c>
       <c r="Z12" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1">
         <v>3</v>
       </c>
-      <c r="AC12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>1</v>
+      <c r="AH12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>6</v>
       </c>
       <c r="AK12" s="1">
         <v>1</v>
@@ -2421,17 +2661,17 @@
         <v>1</v>
       </c>
       <c r="AN12" s="1">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AO12" s="1">
         <v>1</v>
       </c>
       <c r="AP12" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AQ12" s="6">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AR12" s="1" t="s">
         <v>15</v>
@@ -2439,20 +2679,32 @@
       <c r="AS12" s="1">
         <v>1</v>
       </c>
+      <c r="AT12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG12" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:59">
       <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
@@ -2460,31 +2712,46 @@
         <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="1">
         <v>1</v>
       </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
       <c r="J13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1">
-        <v>-2</v>
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
       </c>
-      <c r="S13" s="1">
-        <v>1</v>
-      </c>
-      <c r="T13" s="1">
-        <v>2</v>
-      </c>
-      <c r="U13" s="1">
-        <v>2</v>
+      <c r="V13" s="1">
+        <v>2</v>
+      </c>
+      <c r="W13" s="1">
+        <v>1</v>
       </c>
       <c r="X13" s="1">
         <v>1</v>
@@ -2508,10 +2775,10 @@
         <v>1</v>
       </c>
       <c r="AF13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG13" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="1">
         <v>1</v>
@@ -2520,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK13" s="1">
         <v>1</v>
@@ -2538,14 +2805,14 @@
         <v>1</v>
       </c>
       <c r="AP13" s="1">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AQ13" s="6">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="AR13" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS13" s="1">
         <v>1</v>
@@ -2553,8 +2820,32 @@
       <c r="AT13" s="1">
         <v>1</v>
       </c>
+      <c r="AU13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="1">
+        <v>2</v>
+      </c>
+      <c r="AW13" s="1">
+        <v>4</v>
+      </c>
+      <c r="AX13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="1">
+        <v>2</v>
+      </c>
+      <c r="AZ13" s="1">
+        <v>1</v>
+      </c>
+      <c r="BA13" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG13" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:59">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -2564,123 +2855,48 @@
       <c r="C14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>5</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>1</v>
-      </c>
-      <c r="N14" s="1">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>2</v>
-      </c>
-      <c r="W14" s="1">
-        <v>1</v>
-      </c>
-      <c r="X14" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="1">
+      <c r="AC14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>3</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP14" s="1">
         <v>10</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="1">
-        <v>2</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AI14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AJ14" s="1">
-        <v>7</v>
-      </c>
-      <c r="AK14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN14" s="1">
-        <v>-5</v>
-      </c>
-      <c r="AO14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP14" s="1">
-        <v>26</v>
       </c>
       <c r="AQ14" s="6">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AR14" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AS14" s="1">
         <v>1</v>
       </c>
-      <c r="AT14" s="1">
+      <c r="BG14" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:44">
+    <row r="15" spans="1:59">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
@@ -2690,310 +2906,361 @@
       <c r="C15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="1">
-        <v>1</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="AM15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="1">
         <v>-5</v>
       </c>
-      <c r="M15" s="1">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>-1</v>
-      </c>
-      <c r="S15" s="1">
-        <v>1</v>
-      </c>
-      <c r="T15" s="1">
-        <v>2</v>
-      </c>
-      <c r="U15" s="1">
-        <v>2</v>
-      </c>
-      <c r="V15" s="1">
-        <v>2</v>
-      </c>
-      <c r="W15" s="1">
-        <v>1</v>
-      </c>
-      <c r="X15" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="1">
-        <v>2</v>
-      </c>
-      <c r="AH15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN15" s="1">
-        <v>0</v>
+      <c r="AO15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>13</v>
       </c>
       <c r="AQ15" s="6">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AR15" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="AS15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AX15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG15" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:45">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:44">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:44">
+      <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AC16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="1">
-        <v>3</v>
-      </c>
-      <c r="AK16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP16" s="1">
-        <v>10</v>
-      </c>
-      <c r="AQ16" s="6">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="AR16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS16" s="1">
-        <v>1</v>
+      <c r="R18" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:46">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:44">
+      <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AN17" s="1">
-        <v>-5</v>
-      </c>
-      <c r="AO17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AP17" s="1">
-        <v>13</v>
-      </c>
-      <c r="AQ17" s="6">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="AR17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AT17" s="1">
-        <v>1</v>
+      <c r="C19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:44">
       <c r="A20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="R20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:44">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="R21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:44">
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="R22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:44">
       <c r="A23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="R23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:44">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="R24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:44">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>51</v>
+      <c r="B25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:44">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="R26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:44">
       <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="B27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>54</v>
       </c>
       <c r="R27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:44">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>56</v>
       </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
       <c r="R28" s="1">
         <v>0</v>
       </c>
+      <c r="S28" s="1">
+        <v>1</v>
+      </c>
+      <c r="T28" s="1">
+        <v>2</v>
+      </c>
+      <c r="U28" s="1">
+        <v>2</v>
+      </c>
+      <c r="V28" s="1">
+        <v>2</v>
+      </c>
+      <c r="X28" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="6">
+        <f>SUM(D28:AP28)</f>
+        <v>34</v>
+      </c>
+      <c r="AR28" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:44">
       <c r="A29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>-5</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
       <c r="R29" s="1">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="S29" s="1">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1">
+        <v>2</v>
+      </c>
+      <c r="U29" s="1">
+        <v>2</v>
+      </c>
+      <c r="V29" s="1">
+        <v>2</v>
+      </c>
+      <c r="W29" s="1">
+        <v>1</v>
+      </c>
+      <c r="X29" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="1">
+        <v>2</v>
+      </c>
+      <c r="AF29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="1">
+        <v>2</v>
+      </c>
+      <c r="AH29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="6">
+        <f>SUM(D29:AP29)</f>
+        <v>22</v>
+      </c>
+      <c r="AR29" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N17" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N15" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
